--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,201 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131389081</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>458739</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7080234</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131389096</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>458493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7080303</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389081</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389096</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4717-2026 artfynd.xlsx
+++ b/artfynd/A 4717-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532079</v>
+        <v>131389096</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458619</v>
+        <v>458493</v>
       </c>
       <c r="R2" t="n">
-        <v>7080230</v>
+        <v>7080303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389081</v>
+        <v>121532079</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,19 +788,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458739</v>
+        <v>458619</v>
       </c>
       <c r="R3" t="n">
-        <v>7080234</v>
+        <v>7080230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,108 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>131389096</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tretjärnrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>458493</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7080303</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
